--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="309">
   <si>
     <t>stream</t>
   </si>
@@ -10873,6 +10873,23 @@
         <v>308</v>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" s="1">
+        <v>567.0</v>
+      </c>
+      <c r="B569" s="1">
+        <v>902.0</v>
+      </c>
+      <c r="C569" s="1">
+        <v>1009.0</v>
+      </c>
+      <c r="D569" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="E569" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="309">
   <si>
     <t>stream</t>
   </si>
@@ -10878,7 +10878,7 @@
         <v>567.0</v>
       </c>
       <c r="B569" s="1">
-        <v>902.0</v>
+        <v>899.0</v>
       </c>
       <c r="C569" s="1">
         <v>1009.0</v>
@@ -10888,6 +10888,23 @@
       </c>
       <c r="E569" s="1" t="s">
         <v>304</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1">
+        <v>568.0</v>
+      </c>
+      <c r="B570" s="1">
+        <v>818.0</v>
+      </c>
+      <c r="C570" s="1">
+        <v>965.0</v>
+      </c>
+      <c r="D570" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="E570" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="309">
   <si>
     <t>stream</t>
   </si>
@@ -10907,6 +10907,23 @@
         <v>303</v>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="1">
+        <v>569.0</v>
+      </c>
+      <c r="B571" s="1">
+        <v>794.0</v>
+      </c>
+      <c r="C571" s="1">
+        <v>964.0</v>
+      </c>
+      <c r="D571" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="E571" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="309">
   <si>
     <t>stream</t>
   </si>
@@ -10924,6 +10924,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" s="1">
+        <v>570.0</v>
+      </c>
+      <c r="B572" s="1">
+        <v>942.0</v>
+      </c>
+      <c r="C572" s="1">
+        <v>1582.0</v>
+      </c>
+      <c r="D572" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="E572" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="310">
   <si>
     <t>stream</t>
   </si>
@@ -938,6 +938,9 @@
   </si>
   <si>
     <t>jc, re9</t>
+  </si>
+  <si>
+    <t>jc, lol, golf</t>
   </si>
 </sst>
 </file>
@@ -10941,6 +10944,26 @@
         <v>303</v>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="1">
+        <v>571.0</v>
+      </c>
+      <c r="B573" s="1">
+        <v>772.0</v>
+      </c>
+      <c r="C573" s="1">
+        <v>970.0</v>
+      </c>
+      <c r="D573" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="E573" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="310">
   <si>
     <t>stream</t>
   </si>
@@ -10962,7 +10962,21 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1"/>
+      <c r="A574" s="1">
+        <v>572.0</v>
+      </c>
+      <c r="B574" s="1">
+        <v>1214.0</v>
+      </c>
+      <c r="C574" s="1">
+        <v>1885.0</v>
+      </c>
+      <c r="D574" s="1">
+        <v>466.0</v>
+      </c>
+      <c r="E574" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="311">
   <si>
     <t>stream</t>
   </si>
@@ -941,6 +941,9 @@
   </si>
   <si>
     <t>jc, lol, golf</t>
+  </si>
+  <si>
+    <t>jc, schedule1</t>
   </si>
 </sst>
 </file>
@@ -10978,6 +10981,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="1">
+        <v>573.0</v>
+      </c>
+      <c r="B575" s="1">
+        <v>893.0</v>
+      </c>
+      <c r="C575" s="1">
+        <v>1073.0</v>
+      </c>
+      <c r="D575" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="E575" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="311">
   <si>
     <t>stream</t>
   </si>
@@ -10998,6 +10998,23 @@
         <v>310</v>
       </c>
     </row>
+    <row r="576">
+      <c r="A576" s="1">
+        <v>574.0</v>
+      </c>
+      <c r="B576" s="1">
+        <v>1118.0</v>
+      </c>
+      <c r="C576" s="1">
+        <v>1279.0</v>
+      </c>
+      <c r="D576" s="1">
+        <v>184.0</v>
+      </c>
+      <c r="E576" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="311">
   <si>
     <t>stream</t>
   </si>
@@ -11015,6 +11015,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" s="1">
+        <v>575.0</v>
+      </c>
+      <c r="B577" s="1">
+        <v>880.0</v>
+      </c>
+      <c r="C577" s="1">
+        <v>1037.0</v>
+      </c>
+      <c r="D577" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="E577" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="312">
   <si>
     <t>stream</t>
   </si>
@@ -944,6 +944,9 @@
   </si>
   <si>
     <t>jc, schedule1</t>
+  </si>
+  <si>
+    <t>jc, tf2, cs</t>
   </si>
 </sst>
 </file>
@@ -11032,6 +11035,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="1">
+        <v>576.0</v>
+      </c>
+      <c r="B578" s="1">
+        <v>852.0</v>
+      </c>
+      <c r="C578" s="1">
+        <v>1220.0</v>
+      </c>
+      <c r="D578" s="1">
+        <v>111.0</v>
+      </c>
+      <c r="E578" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="312">
   <si>
     <t>stream</t>
   </si>
@@ -946,7 +946,7 @@
     <t>jc, schedule1</t>
   </si>
   <si>
-    <t>jc, tf2, cs</t>
+    <t>jc, tf2, mc, cs</t>
   </si>
 </sst>
 </file>
@@ -11053,7 +11053,38 @@
       </c>
     </row>
     <row r="579">
-      <c r="B579" s="1"/>
+      <c r="A579" s="1">
+        <v>577.0</v>
+      </c>
+      <c r="B579" s="1">
+        <v>846.0</v>
+      </c>
+      <c r="C579" s="1">
+        <v>1056.0</v>
+      </c>
+      <c r="D579" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="E579" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1">
+        <v>578.0</v>
+      </c>
+      <c r="B580" s="1">
+        <v>1170.0</v>
+      </c>
+      <c r="C580" s="1">
+        <v>1401.0</v>
+      </c>
+      <c r="D580" s="1">
+        <v>183.0</v>
+      </c>
+      <c r="E580" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="313">
   <si>
     <t>stream</t>
   </si>
@@ -947,6 +947,9 @@
   </si>
   <si>
     <t>jc, tf2, mc, cs</t>
+  </si>
+  <si>
+    <t>jc, ds, cs</t>
   </si>
 </sst>
 </file>
@@ -11086,6 +11089,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" s="1">
+        <v>579.0</v>
+      </c>
+      <c r="B581" s="1">
+        <v>1008.0</v>
+      </c>
+      <c r="C581" s="1">
+        <v>1257.0</v>
+      </c>
+      <c r="D581" s="1">
+        <v>140.0</v>
+      </c>
+      <c r="E581" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="313">
   <si>
     <t>stream</t>
   </si>
@@ -11106,6 +11106,23 @@
         <v>312</v>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" s="1">
+        <v>580.0</v>
+      </c>
+      <c r="B582" s="1">
+        <v>1146.0</v>
+      </c>
+      <c r="C582" s="1">
+        <v>2056.0</v>
+      </c>
+      <c r="D582" s="1">
+        <v>170.0</v>
+      </c>
+      <c r="E582" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="313">
   <si>
     <t>stream</t>
   </si>
@@ -11123,6 +11123,26 @@
         <v>231</v>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" s="1">
+        <v>581.0</v>
+      </c>
+      <c r="B583" s="1">
+        <v>1143.0</v>
+      </c>
+      <c r="C583" s="1">
+        <v>1263.0</v>
+      </c>
+      <c r="D583" s="1">
+        <v>240.0</v>
+      </c>
+      <c r="E583" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="314">
   <si>
     <t>stream</t>
   </si>
@@ -950,6 +950,9 @@
   </si>
   <si>
     <t>jc, ds, cs</t>
+  </si>
+  <si>
+    <t>jc, pubg, cs</t>
   </si>
 </sst>
 </file>
@@ -11141,7 +11144,21 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1"/>
+      <c r="A584" s="1">
+        <v>582.0</v>
+      </c>
+      <c r="B584" s="1">
+        <v>958.0</v>
+      </c>
+      <c r="C584" s="1">
+        <v>1141.0</v>
+      </c>
+      <c r="D584" s="1">
+        <v>145.0</v>
+      </c>
+      <c r="E584" s="1" t="s">
+        <v>313</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="314">
   <si>
     <t>stream</t>
   </si>
@@ -11160,6 +11160,23 @@
         <v>313</v>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" s="1">
+        <v>583.0</v>
+      </c>
+      <c r="B585" s="1">
+        <v>1415.0</v>
+      </c>
+      <c r="C585" s="1">
+        <v>1643.0</v>
+      </c>
+      <c r="D585" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="E585" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="315">
   <si>
     <t>stream</t>
   </si>
@@ -953,6 +953,9 @@
   </si>
   <si>
     <t>jc, pubg, cs</t>
+  </si>
+  <si>
+    <t>jc, fallguys, mc, cs</t>
   </si>
 </sst>
 </file>
@@ -11177,6 +11180,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" s="1">
+        <v>584.0</v>
+      </c>
+      <c r="B586" s="1">
+        <v>1275.0</v>
+      </c>
+      <c r="C586" s="1">
+        <v>3952.0</v>
+      </c>
+      <c r="D586" s="1">
+        <v>421.0</v>
+      </c>
+      <c r="E586" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="315">
   <si>
     <t>stream</t>
   </si>
@@ -11197,6 +11197,23 @@
         <v>314</v>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="1">
+        <v>585.0</v>
+      </c>
+      <c r="B587" s="1">
+        <v>986.0</v>
+      </c>
+      <c r="C587" s="1">
+        <v>1261.0</v>
+      </c>
+      <c r="D587" s="1">
+        <v>127.0</v>
+      </c>
+      <c r="E587" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="315">
   <si>
     <t>stream</t>
   </si>
@@ -11214,6 +11214,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" s="1">
+        <v>586.0</v>
+      </c>
+      <c r="B588" s="1">
+        <v>1092.0</v>
+      </c>
+      <c r="C588" s="1">
+        <v>1420.0</v>
+      </c>
+      <c r="D588" s="1">
+        <v>125.0</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="316">
   <si>
     <t>stream</t>
   </si>
@@ -956,6 +956,9 @@
   </si>
   <si>
     <t>jc, fallguys, mc, cs</t>
+  </si>
+  <si>
+    <t>jc, pubg</t>
   </si>
 </sst>
 </file>
@@ -9739,7 +9742,7 @@
         <v>499.0</v>
       </c>
       <c r="B501" s="1">
-        <v>1253.0</v>
+        <v>1259.0</v>
       </c>
       <c r="C501" s="1">
         <v>1492.0</v>
@@ -9807,7 +9810,7 @@
         <v>503.0</v>
       </c>
       <c r="B505" s="1">
-        <v>1111.0</v>
+        <v>1112.0</v>
       </c>
       <c r="C505" s="1">
         <v>1325.0</v>
@@ -11032,7 +11035,7 @@
         <v>575.0</v>
       </c>
       <c r="B577" s="1">
-        <v>880.0</v>
+        <v>910.0</v>
       </c>
       <c r="C577" s="1">
         <v>1037.0</v>
@@ -11083,7 +11086,7 @@
         <v>578.0</v>
       </c>
       <c r="B580" s="1">
-        <v>1170.0</v>
+        <v>1179.0</v>
       </c>
       <c r="C580" s="1">
         <v>1401.0</v>
@@ -11100,7 +11103,7 @@
         <v>579.0</v>
       </c>
       <c r="B581" s="1">
-        <v>1008.0</v>
+        <v>1012.0</v>
       </c>
       <c r="C581" s="1">
         <v>1257.0</v>
@@ -11117,7 +11120,7 @@
         <v>580.0</v>
       </c>
       <c r="B582" s="1">
-        <v>1146.0</v>
+        <v>1147.0</v>
       </c>
       <c r="C582" s="1">
         <v>2056.0</v>
@@ -11134,7 +11137,7 @@
         <v>581.0</v>
       </c>
       <c r="B583" s="1">
-        <v>1143.0</v>
+        <v>1144.0</v>
       </c>
       <c r="C583" s="1">
         <v>1263.0</v>
@@ -11151,7 +11154,7 @@
         <v>582.0</v>
       </c>
       <c r="B584" s="1">
-        <v>958.0</v>
+        <v>966.0</v>
       </c>
       <c r="C584" s="1">
         <v>1141.0</v>
@@ -11185,7 +11188,7 @@
         <v>584.0</v>
       </c>
       <c r="B586" s="1">
-        <v>1275.0</v>
+        <v>1280.0</v>
       </c>
       <c r="C586" s="1">
         <v>3952.0</v>
@@ -11219,7 +11222,7 @@
         <v>586.0</v>
       </c>
       <c r="B588" s="1">
-        <v>1092.0</v>
+        <v>1101.0</v>
       </c>
       <c r="C588" s="1">
         <v>1420.0</v>
@@ -11229,6 +11232,23 @@
       </c>
       <c r="E588" s="1" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1">
+        <v>587.0</v>
+      </c>
+      <c r="B589" s="1">
+        <v>1125.0</v>
+      </c>
+      <c r="C589" s="1">
+        <v>1339.0</v>
+      </c>
+      <c r="D589" s="1">
+        <v>163.0</v>
+      </c>
+      <c r="E589" s="1" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="317">
   <si>
     <t>stream</t>
   </si>
@@ -959,6 +959,9 @@
   </si>
   <si>
     <t>jc, pubg</t>
+  </si>
+  <si>
+    <t>jc, fallguys, mc, skribbl</t>
   </si>
 </sst>
 </file>
@@ -11251,6 +11254,23 @@
         <v>315</v>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" s="1">
+        <v>588.0</v>
+      </c>
+      <c r="B590" s="1">
+        <v>945.0</v>
+      </c>
+      <c r="C590" s="1">
+        <v>1155.0</v>
+      </c>
+      <c r="D590" s="1">
+        <v>181.0</v>
+      </c>
+      <c r="E590" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="318">
   <si>
     <t>stream</t>
   </si>
@@ -962,6 +962,9 @@
   </si>
   <si>
     <t>jc, fallguys, mc, skribbl</t>
+  </si>
+  <si>
+    <t>jc, ftf</t>
   </si>
 </sst>
 </file>
@@ -11271,6 +11274,23 @@
         <v>316</v>
       </c>
     </row>
+    <row r="591">
+      <c r="A591" s="1">
+        <v>589.0</v>
+      </c>
+      <c r="B591" s="1">
+        <v>1461.0</v>
+      </c>
+      <c r="C591" s="1">
+        <v>1887.0</v>
+      </c>
+      <c r="D591" s="1">
+        <v>187.0</v>
+      </c>
+      <c r="E591" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="319">
   <si>
     <t>stream</t>
   </si>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>jc, ftf</t>
+  </si>
+  <si>
+    <t>jc, tf2, pubg</t>
   </si>
 </sst>
 </file>
@@ -11291,6 +11294,23 @@
         <v>317</v>
       </c>
     </row>
+    <row r="592">
+      <c r="A592" s="1">
+        <v>590.0</v>
+      </c>
+      <c r="B592" s="1">
+        <v>1307.0</v>
+      </c>
+      <c r="C592" s="1">
+        <v>1456.0</v>
+      </c>
+      <c r="D592" s="1">
+        <v>217.0</v>
+      </c>
+      <c r="E592" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="320">
   <si>
     <t>stream</t>
   </si>
@@ -968,6 +968,9 @@
   </si>
   <si>
     <t>jc, tf2, pubg</t>
+  </si>
+  <si>
+    <t>jc, liarsbar, cs</t>
   </si>
 </sst>
 </file>
@@ -11311,6 +11314,23 @@
         <v>318</v>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" s="1">
+        <v>591.0</v>
+      </c>
+      <c r="B593" s="1">
+        <v>1284.0</v>
+      </c>
+      <c r="C593" s="1">
+        <v>1781.0</v>
+      </c>
+      <c r="D593" s="1">
+        <v>316.0</v>
+      </c>
+      <c r="E593" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="320">
   <si>
     <t>stream</t>
   </si>
@@ -11331,6 +11331,23 @@
         <v>319</v>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" s="1">
+        <v>592.0</v>
+      </c>
+      <c r="B594" s="1">
+        <v>938.0</v>
+      </c>
+      <c r="C594" s="1">
+        <v>1012.0</v>
+      </c>
+      <c r="D594" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="E594" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="320">
   <si>
     <t>stream</t>
   </si>
@@ -11348,6 +11348,23 @@
         <v>15</v>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" s="1">
+        <v>593.0</v>
+      </c>
+      <c r="B595" s="1">
+        <v>1516.0</v>
+      </c>
+      <c r="C595" s="1">
+        <v>1954.0</v>
+      </c>
+      <c r="D595" s="1">
+        <v>185.0</v>
+      </c>
+      <c r="E595" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="320">
   <si>
     <t>stream</t>
   </si>
@@ -11365,6 +11365,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="596">
+      <c r="A596" s="1">
+        <v>594.0</v>
+      </c>
+      <c r="B596" s="1">
+        <v>1249.0</v>
+      </c>
+      <c r="C596" s="1">
+        <v>1501.0</v>
+      </c>
+      <c r="D596" s="1">
+        <v>154.0</v>
+      </c>
+      <c r="E596" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="320">
   <si>
     <t>stream</t>
   </si>
@@ -11382,6 +11382,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" s="1">
+        <v>595.0</v>
+      </c>
+      <c r="B597" s="1">
+        <v>1248.0</v>
+      </c>
+      <c r="C597" s="1">
+        <v>1809.0</v>
+      </c>
+      <c r="D597" s="1">
+        <v>193.0</v>
+      </c>
+      <c r="E597" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1">
+        <v>596.0</v>
+      </c>
+      <c r="B598" s="1">
+        <v>1197.0</v>
+      </c>
+      <c r="C598" s="1">
+        <v>1433.0</v>
+      </c>
+      <c r="D598" s="1">
+        <v>362.0</v>
+      </c>
+      <c r="E598" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="321">
   <si>
     <t>stream</t>
   </si>
@@ -971,6 +971,9 @@
   </si>
   <si>
     <t>jc, liarsbar, cs</t>
+  </si>
+  <si>
+    <t>jc, samson</t>
   </si>
 </sst>
 </file>
@@ -11416,6 +11419,40 @@
         <v>153</v>
       </c>
     </row>
+    <row r="599">
+      <c r="A599" s="1">
+        <v>597.0</v>
+      </c>
+      <c r="B599" s="1">
+        <v>1132.0</v>
+      </c>
+      <c r="C599" s="1">
+        <v>1325.0</v>
+      </c>
+      <c r="D599" s="1">
+        <v>160.0</v>
+      </c>
+      <c r="E599" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1">
+        <v>598.0</v>
+      </c>
+      <c r="B600" s="1">
+        <v>1205.0</v>
+      </c>
+      <c r="C600" s="1">
+        <v>1506.0</v>
+      </c>
+      <c r="D600" s="1">
+        <v>136.0</v>
+      </c>
+      <c r="E600" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="321">
   <si>
     <t>stream</t>
   </si>
@@ -11453,6 +11453,40 @@
         <v>320</v>
       </c>
     </row>
+    <row r="601">
+      <c r="A601" s="1">
+        <v>599.0</v>
+      </c>
+      <c r="B601" s="1">
+        <v>1182.0</v>
+      </c>
+      <c r="C601" s="1">
+        <v>1882.0</v>
+      </c>
+      <c r="D601" s="1">
+        <v>341.0</v>
+      </c>
+      <c r="E601" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1">
+        <v>600.0</v>
+      </c>
+      <c r="B602" s="1">
+        <v>1083.0</v>
+      </c>
+      <c r="C602" s="1">
+        <v>1439.0</v>
+      </c>
+      <c r="D602" s="1">
+        <v>152.0</v>
+      </c>
+      <c r="E602" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -964,7 +964,7 @@
     <t>jc, fallguys, mc, skribbl</t>
   </si>
   <si>
-    <t>jc, ftf</t>
+    <t>jc, ftfL</t>
   </si>
   <si>
     <t>jc, tf2, pubg</t>
@@ -974,6 +974,9 @@
   </si>
   <si>
     <t>jc, samson</t>
+  </si>
+  <si>
+    <t>jc, ftfW, cs</t>
   </si>
 </sst>
 </file>
@@ -11487,6 +11490,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" s="1">
+        <v>601.0</v>
+      </c>
+      <c r="B603" s="1">
+        <v>1460.0</v>
+      </c>
+      <c r="C603" s="1">
+        <v>2061.0</v>
+      </c>
+      <c r="D603" s="1">
+        <v>197.0</v>
+      </c>
+      <c r="E603" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11495,7 +11495,7 @@
         <v>601.0</v>
       </c>
       <c r="B603" s="1">
-        <v>1460.0</v>
+        <v>1475.0</v>
       </c>
       <c r="C603" s="1">
         <v>2061.0</v>
@@ -11505,6 +11505,23 @@
       </c>
       <c r="E603" s="1" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1">
+        <v>602.0</v>
+      </c>
+      <c r="B604" s="1">
+        <v>1292.0</v>
+      </c>
+      <c r="C604" s="1">
+        <v>1598.0</v>
+      </c>
+      <c r="D604" s="1">
+        <v>197.0</v>
+      </c>
+      <c r="E604" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11524,6 +11524,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" s="1">
+        <v>603.0</v>
+      </c>
+      <c r="B605" s="1">
+        <v>1384.0</v>
+      </c>
+      <c r="C605" s="1">
+        <v>1611.0</v>
+      </c>
+      <c r="D605" s="1">
+        <v>187.0</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1">
+        <v>604.0</v>
+      </c>
+      <c r="B606" s="1">
+        <v>1448.0</v>
+      </c>
+      <c r="C606" s="1">
+        <v>1818.0</v>
+      </c>
+      <c r="D606" s="1">
+        <v>692.0</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11558,6 +11558,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="1">
+        <v>605.0</v>
+      </c>
+      <c r="B607" s="1">
+        <v>1262.0</v>
+      </c>
+      <c r="C607" s="1">
+        <v>1820.0</v>
+      </c>
+      <c r="D607" s="1">
+        <v>240.0</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11575,6 +11575,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" s="1">
+        <v>606.0</v>
+      </c>
+      <c r="B608" s="1">
+        <v>1363.0</v>
+      </c>
+      <c r="C608" s="1">
+        <v>1778.0</v>
+      </c>
+      <c r="D608" s="1">
+        <v>298.0</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11592,6 +11592,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" s="1">
+        <v>607.0</v>
+      </c>
+      <c r="B609" s="1">
+        <v>1600.0</v>
+      </c>
+      <c r="C609" s="1">
+        <v>2180.0</v>
+      </c>
+      <c r="D609" s="1">
+        <v>297.0</v>
+      </c>
+      <c r="E609" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1">
+        <v>608.0</v>
+      </c>
+      <c r="B610" s="1">
+        <v>1603.0</v>
+      </c>
+      <c r="C610" s="1">
+        <v>1894.0</v>
+      </c>
+      <c r="D610" s="1">
+        <v>271.0</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11626,6 +11626,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" s="1">
+        <v>609.0</v>
+      </c>
+      <c r="B611" s="1">
+        <v>1154.0</v>
+      </c>
+      <c r="C611" s="1">
+        <v>1485.0</v>
+      </c>
+      <c r="D611" s="1">
+        <v>216.0</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="322">
   <si>
     <t>stream</t>
   </si>
@@ -11631,16 +11631,33 @@
         <v>609.0</v>
       </c>
       <c r="B611" s="1">
-        <v>1154.0</v>
+        <v>1153.0</v>
       </c>
       <c r="C611" s="1">
         <v>1485.0</v>
       </c>
       <c r="D611" s="1">
-        <v>216.0</v>
+        <v>220.0</v>
       </c>
       <c r="E611" s="1" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1">
+        <v>610.0</v>
+      </c>
+      <c r="B612" s="1">
+        <v>1865.0</v>
+      </c>
+      <c r="C612" s="1">
+        <v>2227.0</v>
+      </c>
+      <c r="D612" s="1">
+        <v>208.0</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="323">
   <si>
     <t>stream</t>
   </si>
@@ -977,6 +977,9 @@
   </si>
   <si>
     <t>jc, ftfW, cs</t>
+  </si>
+  <si>
+    <t>jc, cs, l4d2</t>
   </si>
 </sst>
 </file>
@@ -11660,6 +11663,40 @@
         <v>15</v>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1">
+        <v>611.0</v>
+      </c>
+      <c r="B613" s="1">
+        <v>1789.0</v>
+      </c>
+      <c r="C613" s="1">
+        <v>2972.0</v>
+      </c>
+      <c r="D613" s="1">
+        <v>372.0</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1">
+        <v>612.0</v>
+      </c>
+      <c r="B614" s="1">
+        <v>1696.0</v>
+      </c>
+      <c r="C614" s="1">
+        <v>2557.0</v>
+      </c>
+      <c r="D614" s="1">
+        <v>358.0</v>
+      </c>
+      <c r="E614" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="323">
   <si>
     <t>stream</t>
   </si>
@@ -11697,6 +11697,23 @@
         <v>322</v>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" s="1">
+        <v>613.0</v>
+      </c>
+      <c r="B615" s="1">
+        <v>1649.0</v>
+      </c>
+      <c r="C615" s="1">
+        <v>1965.0</v>
+      </c>
+      <c r="D615" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="323">
   <si>
     <t>stream</t>
   </si>
@@ -11714,6 +11714,23 @@
         <v>322</v>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" s="1">
+        <v>614.0</v>
+      </c>
+      <c r="B616" s="1">
+        <v>1406.0</v>
+      </c>
+      <c r="C616" s="1">
+        <v>1658.0</v>
+      </c>
+      <c r="D616" s="1">
+        <v>219.0</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="323">
   <si>
     <t>stream</t>
   </si>
@@ -11549,7 +11549,7 @@
         <v>604.0</v>
       </c>
       <c r="B606" s="1">
-        <v>1448.0</v>
+        <v>1433.0</v>
       </c>
       <c r="C606" s="1">
         <v>1818.0</v>
@@ -11566,13 +11566,13 @@
         <v>605.0</v>
       </c>
       <c r="B607" s="1">
-        <v>1262.0</v>
+        <v>1395.0</v>
       </c>
       <c r="C607" s="1">
-        <v>1820.0</v>
+        <v>1599.0</v>
       </c>
       <c r="D607" s="1">
-        <v>240.0</v>
+        <v>147.0</v>
       </c>
       <c r="E607" s="1" t="s">
         <v>10</v>
@@ -11583,13 +11583,13 @@
         <v>606.0</v>
       </c>
       <c r="B608" s="1">
-        <v>1363.0</v>
+        <v>1591.0</v>
       </c>
       <c r="C608" s="1">
-        <v>1778.0</v>
+        <v>2164.0</v>
       </c>
       <c r="D608" s="1">
-        <v>298.0</v>
+        <v>263.0</v>
       </c>
       <c r="E608" s="1" t="s">
         <v>10</v>
@@ -11600,16 +11600,16 @@
         <v>607.0</v>
       </c>
       <c r="B609" s="1">
-        <v>1600.0</v>
+        <v>1271.0</v>
       </c>
       <c r="C609" s="1">
-        <v>2180.0</v>
+        <v>1820.0</v>
       </c>
       <c r="D609" s="1">
-        <v>297.0</v>
+        <v>240.0</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>315</v>
+        <v>10</v>
       </c>
     </row>
     <row r="610">
@@ -11617,13 +11617,13 @@
         <v>608.0</v>
       </c>
       <c r="B610" s="1">
-        <v>1603.0</v>
+        <v>1365.0</v>
       </c>
       <c r="C610" s="1">
-        <v>1894.0</v>
+        <v>1778.0</v>
       </c>
       <c r="D610" s="1">
-        <v>271.0</v>
+        <v>298.0</v>
       </c>
       <c r="E610" s="1" t="s">
         <v>10</v>
@@ -11634,16 +11634,16 @@
         <v>609.0</v>
       </c>
       <c r="B611" s="1">
-        <v>1153.0</v>
+        <v>1600.0</v>
       </c>
       <c r="C611" s="1">
-        <v>1485.0</v>
+        <v>2180.0</v>
       </c>
       <c r="D611" s="1">
-        <v>220.0</v>
+        <v>297.0</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>130</v>
+        <v>315</v>
       </c>
     </row>
     <row r="612">
@@ -11651,16 +11651,16 @@
         <v>610.0</v>
       </c>
       <c r="B612" s="1">
-        <v>1865.0</v>
+        <v>1603.0</v>
       </c>
       <c r="C612" s="1">
-        <v>2227.0</v>
+        <v>1894.0</v>
       </c>
       <c r="D612" s="1">
-        <v>208.0</v>
+        <v>271.0</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="613">
@@ -11668,16 +11668,16 @@
         <v>611.0</v>
       </c>
       <c r="B613" s="1">
-        <v>1789.0</v>
+        <v>1153.0</v>
       </c>
       <c r="C613" s="1">
-        <v>2972.0</v>
+        <v>1485.0</v>
       </c>
       <c r="D613" s="1">
-        <v>372.0</v>
+        <v>220.0</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
     </row>
     <row r="614">
@@ -11685,16 +11685,16 @@
         <v>612.0</v>
       </c>
       <c r="B614" s="1">
-        <v>1696.0</v>
+        <v>1865.0</v>
       </c>
       <c r="C614" s="1">
-        <v>2557.0</v>
+        <v>2227.0</v>
       </c>
       <c r="D614" s="1">
-        <v>358.0</v>
+        <v>208.0</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>322</v>
+        <v>15</v>
       </c>
     </row>
     <row r="615">
@@ -11702,13 +11702,13 @@
         <v>613.0</v>
       </c>
       <c r="B615" s="1">
-        <v>1649.0</v>
+        <v>1789.0</v>
       </c>
       <c r="C615" s="1">
-        <v>1965.0</v>
+        <v>2972.0</v>
       </c>
       <c r="D615" s="1">
-        <v>300.0</v>
+        <v>372.0</v>
       </c>
       <c r="E615" s="1" t="s">
         <v>322</v>
@@ -11719,16 +11719,84 @@
         <v>614.0</v>
       </c>
       <c r="B616" s="1">
-        <v>1406.0</v>
+        <v>1696.0</v>
       </c>
       <c r="C616" s="1">
-        <v>1658.0</v>
+        <v>2557.0</v>
       </c>
       <c r="D616" s="1">
-        <v>219.0</v>
+        <v>358.0</v>
       </c>
       <c r="E616" s="1" t="s">
         <v>322</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1">
+        <v>615.0</v>
+      </c>
+      <c r="B617" s="1">
+        <v>1649.0</v>
+      </c>
+      <c r="C617" s="1">
+        <v>1965.0</v>
+      </c>
+      <c r="D617" s="1">
+        <v>300.0</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1">
+        <v>616.0</v>
+      </c>
+      <c r="B618" s="1">
+        <v>1406.0</v>
+      </c>
+      <c r="C618" s="1">
+        <v>1658.0</v>
+      </c>
+      <c r="D618" s="1">
+        <v>219.0</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1">
+        <v>617.0</v>
+      </c>
+      <c r="B619" s="1">
+        <v>1316.0</v>
+      </c>
+      <c r="C619" s="1">
+        <v>1689.0</v>
+      </c>
+      <c r="D619" s="1">
+        <v>136.0</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1">
+        <v>618.0</v>
+      </c>
+      <c r="B620" s="1">
+        <v>1732.0</v>
+      </c>
+      <c r="C620" s="1">
+        <v>2308.0</v>
+      </c>
+      <c r="D620" s="1">
+        <v>250.0</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="324">
   <si>
     <t>stream</t>
   </si>
@@ -980,6 +980,9 @@
   </si>
   <si>
     <t>jc, cs, l4d2</t>
+  </si>
+  <si>
+    <t>jc, marbies, cs</t>
   </si>
 </sst>
 </file>
@@ -11799,6 +11802,23 @@
         <v>76</v>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" s="1">
+        <v>619.0</v>
+      </c>
+      <c r="B621" s="1">
+        <v>1446.0</v>
+      </c>
+      <c r="C621" s="1">
+        <v>1948.0</v>
+      </c>
+      <c r="D621" s="1">
+        <v>176.0</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="325">
   <si>
     <t>stream</t>
   </si>
@@ -983,6 +983,9 @@
   </si>
   <si>
     <t>jc, marbies, cs</t>
+  </si>
+  <si>
+    <t>jc, cs, lol, l4d2</t>
   </si>
 </sst>
 </file>
@@ -11819,6 +11822,23 @@
         <v>323</v>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" s="1">
+        <v>620.0</v>
+      </c>
+      <c r="B622" s="1">
+        <v>1470.0</v>
+      </c>
+      <c r="C622" s="1">
+        <v>1884.0</v>
+      </c>
+      <c r="D622" s="1">
+        <v>123.0</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="325">
   <si>
     <t>stream</t>
   </si>
@@ -11839,6 +11839,23 @@
         <v>324</v>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="1">
+        <v>621.0</v>
+      </c>
+      <c r="B623" s="1">
+        <v>1544.0</v>
+      </c>
+      <c r="C623" s="1">
+        <v>1949.0</v>
+      </c>
+      <c r="D623" s="1">
+        <v>154.0</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="325">
   <si>
     <t>stream</t>
   </si>
@@ -11856,6 +11856,40 @@
         <v>76</v>
       </c>
     </row>
+    <row r="624">
+      <c r="A624" s="1">
+        <v>622.0</v>
+      </c>
+      <c r="B624" s="1">
+        <v>1379.0</v>
+      </c>
+      <c r="C624" s="1">
+        <v>1472.0</v>
+      </c>
+      <c r="D624" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1">
+        <v>623.0</v>
+      </c>
+      <c r="B625" s="1">
+        <v>1379.0</v>
+      </c>
+      <c r="C625" s="1">
+        <v>1947.0</v>
+      </c>
+      <c r="D625" s="1">
+        <v>412.0</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="325">
   <si>
     <t>stream</t>
   </si>
@@ -11890,6 +11890,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="1">
+        <v>624.0</v>
+      </c>
+      <c r="B626" s="1">
+        <v>1757.0</v>
+      </c>
+      <c r="C626" s="1">
+        <v>2405.0</v>
+      </c>
+      <c r="D626" s="1">
+        <v>189.0</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="326">
   <si>
     <t>stream</t>
   </si>
@@ -986,6 +986,9 @@
   </si>
   <si>
     <t>jc, cs, lol, l4d2</t>
+  </si>
+  <si>
+    <t>jc, fallguys, lol</t>
   </si>
 </sst>
 </file>
@@ -11907,6 +11910,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" s="1">
+        <v>625.0</v>
+      </c>
+      <c r="B627" s="1">
+        <v>1123.0</v>
+      </c>
+      <c r="C627" s="1">
+        <v>1225.0</v>
+      </c>
+      <c r="D627" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -989,6 +989,9 @@
   </si>
   <si>
     <t>jc, fallguys, lol</t>
+  </si>
+  <si>
+    <t>jc, pubg, fallguys</t>
   </si>
 </sst>
 </file>
@@ -11927,6 +11930,40 @@
         <v>325</v>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" s="1">
+        <v>626.0</v>
+      </c>
+      <c r="B628" s="1">
+        <v>1306.0</v>
+      </c>
+      <c r="C628" s="1">
+        <v>1587.0</v>
+      </c>
+      <c r="D628" s="1">
+        <v>194.0</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1">
+        <v>627.0</v>
+      </c>
+      <c r="B629" s="1">
+        <v>1306.0</v>
+      </c>
+      <c r="C629" s="1">
+        <v>1779.0</v>
+      </c>
+      <c r="D629" s="1">
+        <v>169.0</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -11964,6 +11964,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="1">
+        <v>628.0</v>
+      </c>
+      <c r="B630" s="1">
+        <v>1672.0</v>
+      </c>
+      <c r="C630" s="1">
+        <v>1969.0</v>
+      </c>
+      <c r="D630" s="1">
+        <v>154.0</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -11981,6 +11981,23 @@
         <v>76</v>
       </c>
     </row>
+    <row r="631">
+      <c r="A631" s="1">
+        <v>629.0</v>
+      </c>
+      <c r="B631" s="1">
+        <v>1357.0</v>
+      </c>
+      <c r="C631" s="1">
+        <v>1561.0</v>
+      </c>
+      <c r="D631" s="1">
+        <v>132.0</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -11998,6 +11998,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" s="1">
+        <v>630.0</v>
+      </c>
+      <c r="B632" s="1">
+        <v>1263.0</v>
+      </c>
+      <c r="C632" s="1">
+        <v>1604.0</v>
+      </c>
+      <c r="D632" s="1">
+        <v>152.0</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -12015,6 +12015,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" s="1">
+        <v>631.0</v>
+      </c>
+      <c r="B633" s="1">
+        <v>1242.0</v>
+      </c>
+      <c r="C633" s="1">
+        <v>1493.0</v>
+      </c>
+      <c r="D633" s="1">
+        <v>114.0</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -1035,7 +1035,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1044,6 +1044,9 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12032,6 +12035,24 @@
         <v>76</v>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" s="1">
+        <v>632.0</v>
+      </c>
+      <c r="B634" s="1">
+        <v>1445.0</v>
+      </c>
+      <c r="C634" s="1">
+        <v>1628.0</v>
+      </c>
+      <c r="D634" s="1">
+        <v>149.0</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F634" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -12053,6 +12053,23 @@
       </c>
       <c r="F634" s="3"/>
     </row>
+    <row r="635">
+      <c r="A635" s="1">
+        <v>633.0</v>
+      </c>
+      <c r="B635" s="1">
+        <v>1577.0</v>
+      </c>
+      <c r="C635" s="1">
+        <v>1827.0</v>
+      </c>
+      <c r="D635" s="1">
+        <v>215.0</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -12070,6 +12070,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1">
+        <v>634.0</v>
+      </c>
+      <c r="B636" s="1">
+        <v>1506.0</v>
+      </c>
+      <c r="C636" s="1">
+        <v>1851.0</v>
+      </c>
+      <c r="D636" s="1">
+        <v>139.0</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -12087,6 +12087,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" s="1">
+        <v>635.0</v>
+      </c>
+      <c r="B637" s="1">
+        <v>1221.0</v>
+      </c>
+      <c r="C637" s="1">
+        <v>1494.0</v>
+      </c>
+      <c r="D637" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="327">
   <si>
     <t>stream</t>
   </si>
@@ -12104,6 +12104,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1">
+        <v>636.0</v>
+      </c>
+      <c r="B638" s="1">
+        <v>1454.0</v>
+      </c>
+      <c r="C638" s="1">
+        <v>2846.0</v>
+      </c>
+      <c r="D638" s="1">
+        <v>342.0</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="328">
   <si>
     <t>stream</t>
   </si>
@@ -992,6 +992,9 @@
   </si>
   <si>
     <t>jc, pubg, fallguys</t>
+  </si>
+  <si>
+    <t>jc, roblox, ftfN</t>
   </si>
 </sst>
 </file>
@@ -12121,6 +12124,23 @@
         <v>37</v>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" s="1">
+        <v>637.0</v>
+      </c>
+      <c r="B639" s="1">
+        <v>1424.0</v>
+      </c>
+      <c r="C639" s="1">
+        <v>1687.0</v>
+      </c>
+      <c r="D639" s="1">
+        <v>99.0</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="328">
   <si>
     <t>stream</t>
   </si>
@@ -12141,6 +12141,23 @@
         <v>327</v>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" s="1">
+        <v>638.0</v>
+      </c>
+      <c r="B640" s="1">
+        <v>1564.0</v>
+      </c>
+      <c r="C640" s="1">
+        <v>1844.0</v>
+      </c>
+      <c r="D640" s="1">
+        <v>156.0</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="329">
   <si>
     <t>stream</t>
   </si>
@@ -995,6 +995,9 @@
   </si>
   <si>
     <t>jc, roblox, ftfN</t>
+  </si>
+  <si>
+    <t>jc, mc, 007</t>
   </si>
 </sst>
 </file>
@@ -12158,6 +12161,24 @@
         <v>10</v>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="1">
+        <v>639.0</v>
+      </c>
+      <c r="B641" s="1">
+        <v>1285.0</v>
+      </c>
+      <c r="C641" s="1">
+        <v>1455.0</v>
+      </c>
+      <c r="D641" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F641" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="330">
   <si>
     <t>stream</t>
   </si>
@@ -998,6 +998,9 @@
   </si>
   <si>
     <t>jc, mc, 007</t>
+  </si>
+  <si>
+    <t>jc, 007</t>
   </si>
 </sst>
 </file>
@@ -12166,18 +12169,53 @@
         <v>639.0</v>
       </c>
       <c r="B641" s="1">
-        <v>1285.0</v>
+        <v>1186.0</v>
       </c>
       <c r="C641" s="1">
-        <v>1455.0</v>
+        <v>1461.0</v>
       </c>
       <c r="D641" s="1">
-        <v>106.0</v>
+        <v>129.0</v>
       </c>
       <c r="E641" s="1" t="s">
         <v>328</v>
       </c>
       <c r="F641" s="1"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="1">
+        <v>640.0</v>
+      </c>
+      <c r="B642" s="1">
+        <v>1285.0</v>
+      </c>
+      <c r="C642" s="1">
+        <v>1455.0</v>
+      </c>
+      <c r="D642" s="1">
+        <v>106.0</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F642" s="1"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="1">
+        <v>641.0</v>
+      </c>
+      <c r="B643" s="1">
+        <v>1682.0</v>
+      </c>
+      <c r="C643" s="1">
+        <v>1983.0</v>
+      </c>
+      <c r="D643" s="1">
+        <v>120.0</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="331">
   <si>
     <t>stream</t>
   </si>
@@ -1001,6 +1001,9 @@
   </si>
   <si>
     <t>jc, 007</t>
+  </si>
+  <si>
+    <t>wot</t>
   </si>
 </sst>
 </file>
@@ -12217,6 +12220,23 @@
         <v>27</v>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" s="1">
+        <v>642.0</v>
+      </c>
+      <c r="B644" s="1">
+        <v>1018.0</v>
+      </c>
+      <c r="C644" s="1">
+        <v>1096.0</v>
+      </c>
+      <c r="D644" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="331">
   <si>
     <t>stream</t>
   </si>
@@ -12237,6 +12237,23 @@
         <v>330</v>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" s="1">
+        <v>643.0</v>
+      </c>
+      <c r="B645" s="1">
+        <v>1466.0</v>
+      </c>
+      <c r="C645" s="1">
+        <v>1790.0</v>
+      </c>
+      <c r="D645" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="331">
   <si>
     <t>stream</t>
   </si>
@@ -12254,6 +12254,23 @@
         <v>27</v>
       </c>
     </row>
+    <row r="646">
+      <c r="A646" s="1">
+        <v>644.0</v>
+      </c>
+      <c r="B646" s="1">
+        <v>1212.0</v>
+      </c>
+      <c r="C646" s="1">
+        <v>1399.0</v>
+      </c>
+      <c r="D646" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="331">
   <si>
     <t>stream</t>
   </si>
@@ -12271,6 +12271,23 @@
         <v>37</v>
       </c>
     </row>
+    <row r="647">
+      <c r="A647" s="1">
+        <v>645.0</v>
+      </c>
+      <c r="B647" s="1">
+        <v>1254.0</v>
+      </c>
+      <c r="C647" s="1">
+        <v>1695.0</v>
+      </c>
+      <c r="D647" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="331">
   <si>
     <t>stream</t>
   </si>
@@ -12288,6 +12288,23 @@
         <v>329</v>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" s="1">
+        <v>646.0</v>
+      </c>
+      <c r="B648" s="1">
+        <v>1032.0</v>
+      </c>
+      <c r="C648" s="1">
+        <v>1135.0</v>
+      </c>
+      <c r="D648" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="332">
   <si>
     <t>stream</t>
   </si>
@@ -1004,6 +1004,9 @@
   </si>
   <si>
     <t>wot</t>
+  </si>
+  <si>
+    <t>jc, cs, fallguys, special</t>
   </si>
 </sst>
 </file>
@@ -12305,6 +12308,23 @@
         <v>329</v>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" s="1">
+        <v>647.0</v>
+      </c>
+      <c r="B649" s="1">
+        <v>1102.0</v>
+      </c>
+      <c r="C649" s="1">
+        <v>1273.0</v>
+      </c>
+      <c r="D649" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="333">
   <si>
     <t>stream</t>
   </si>
@@ -1007,6 +1007,9 @@
   </si>
   <si>
     <t>jc, cs, fallguys, special</t>
+  </si>
+  <si>
+    <t>jc, special, marbels, lol</t>
   </si>
 </sst>
 </file>
@@ -12325,6 +12328,40 @@
         <v>331</v>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" s="1">
+        <v>648.0</v>
+      </c>
+      <c r="B650" s="1">
+        <v>1242.0</v>
+      </c>
+      <c r="C650" s="1">
+        <v>1703.0</v>
+      </c>
+      <c r="D650" s="1">
+        <v>110.0</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1">
+        <v>649.0</v>
+      </c>
+      <c r="B651" s="1">
+        <v>1052.0</v>
+      </c>
+      <c r="C651" s="1">
+        <v>1286.0</v>
+      </c>
+      <c r="D651" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="334">
   <si>
     <t>stream</t>
   </si>
@@ -1010,6 +1010,9 @@
   </si>
   <si>
     <t>jc, special, marbels, lol</t>
+  </si>
+  <si>
+    <t>jc, ftfC, ftfS</t>
   </si>
 </sst>
 </file>
@@ -12362,6 +12365,23 @@
         <v>332</v>
       </c>
     </row>
+    <row r="652">
+      <c r="A652" s="1">
+        <v>650.0</v>
+      </c>
+      <c r="B652" s="1">
+        <v>981.0</v>
+      </c>
+      <c r="C652" s="1">
+        <v>1148.0</v>
+      </c>
+      <c r="D652" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="335">
   <si>
     <t>stream</t>
   </si>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>jc, ftfC, ftfS</t>
+  </si>
+  <si>
+    <t>jc, cs, hvr</t>
   </si>
 </sst>
 </file>
@@ -12382,6 +12385,23 @@
         <v>333</v>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" s="1">
+        <v>651.0</v>
+      </c>
+      <c r="B653" s="1">
+        <v>1135.0</v>
+      </c>
+      <c r="C653" s="1">
+        <v>1409.0</v>
+      </c>
+      <c r="D653" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="335">
   <si>
     <t>stream</t>
   </si>
@@ -12402,6 +12402,23 @@
         <v>334</v>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" s="1">
+        <v>652.0</v>
+      </c>
+      <c r="B654" s="1">
+        <v>1131.0</v>
+      </c>
+      <c r="C654" s="1">
+        <v>1855.0</v>
+      </c>
+      <c r="D654" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="336">
   <si>
     <t>stream</t>
   </si>
@@ -1016,6 +1016,9 @@
   </si>
   <si>
     <t>jc, cs, hvr</t>
+  </si>
+  <si>
+    <t>jc, hvr</t>
   </si>
 </sst>
 </file>
@@ -12419,6 +12422,40 @@
         <v>334</v>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" s="1">
+        <v>653.0</v>
+      </c>
+      <c r="B655" s="1">
+        <v>1244.0</v>
+      </c>
+      <c r="C655" s="1">
+        <v>1980.0</v>
+      </c>
+      <c r="D655" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1">
+        <v>654.0</v>
+      </c>
+      <c r="B656" s="1">
+        <v>1143.0</v>
+      </c>
+      <c r="C656" s="1">
+        <v>1468.0</v>
+      </c>
+      <c r="D656" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="337">
   <si>
     <t>stream</t>
   </si>
@@ -1019,6 +1019,9 @@
   </si>
   <si>
     <t>jc, hvr</t>
+  </si>
+  <si>
+    <t>jc, chameleon</t>
   </si>
 </sst>
 </file>
@@ -12456,6 +12459,23 @@
         <v>15</v>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" s="1">
+        <v>655.0</v>
+      </c>
+      <c r="B657" s="1">
+        <v>1168.0</v>
+      </c>
+      <c r="C657" s="1">
+        <v>1329.0</v>
+      </c>
+      <c r="D657" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="337">
   <si>
     <t>stream</t>
   </si>
@@ -12476,6 +12476,23 @@
         <v>336</v>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="1">
+        <v>656.0</v>
+      </c>
+      <c r="B658" s="1">
+        <v>1397.0</v>
+      </c>
+      <c r="C658" s="1">
+        <v>1863.0</v>
+      </c>
+      <c r="D658" s="1">
+        <v>290.0</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="337">
   <si>
     <t>stream</t>
   </si>
@@ -12493,6 +12493,23 @@
         <v>267</v>
       </c>
     </row>
+    <row r="659">
+      <c r="A659" s="1">
+        <v>657.0</v>
+      </c>
+      <c r="B659" s="1">
+        <v>1477.0</v>
+      </c>
+      <c r="C659" s="1">
+        <v>1701.0</v>
+      </c>
+      <c r="D659" s="1">
+        <v>126.0</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="337">
   <si>
     <t>stream</t>
   </si>
@@ -12510,6 +12510,24 @@
         <v>10</v>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" s="1">
+        <v>658.0</v>
+      </c>
+      <c r="B660" s="1">
+        <v>1118.0</v>
+      </c>
+      <c r="C660" s="1">
+        <v>1540.0</v>
+      </c>
+      <c r="D660" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F660" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="337">
   <si>
     <t>stream</t>
   </si>
@@ -12528,6 +12528,23 @@
       </c>
       <c r="F660" s="1"/>
     </row>
+    <row r="661">
+      <c r="A661" s="1">
+        <v>659.0</v>
+      </c>
+      <c r="B661" s="1">
+        <v>1397.0</v>
+      </c>
+      <c r="C661" s="1">
+        <v>1662.0</v>
+      </c>
+      <c r="D661" s="1">
+        <v>130.0</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="337">
   <si>
     <t>stream</t>
   </si>
@@ -12545,6 +12545,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" s="1">
+        <v>660.0</v>
+      </c>
+      <c r="B662" s="1">
+        <v>1583.0</v>
+      </c>
+      <c r="C662" s="1">
+        <v>2048.0</v>
+      </c>
+      <c r="D662" s="1">
+        <v>258.0</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="338">
   <si>
     <t>stream</t>
   </si>
@@ -1022,6 +1022,9 @@
   </si>
   <si>
     <t>jc, chameleon</t>
+  </si>
+  <si>
+    <t>jc, wu</t>
   </si>
 </sst>
 </file>
@@ -12562,6 +12565,23 @@
         <v>10</v>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" s="1">
+        <v>661.0</v>
+      </c>
+      <c r="B663" s="1">
+        <v>1347.0</v>
+      </c>
+      <c r="C663" s="1">
+        <v>1611.0</v>
+      </c>
+      <c r="D663" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="338">
   <si>
     <t>stream</t>
   </si>
@@ -12582,6 +12582,40 @@
         <v>337</v>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" s="1">
+        <v>662.0</v>
+      </c>
+      <c r="B664" s="1">
+        <v>1300.0</v>
+      </c>
+      <c r="C664" s="1">
+        <v>169.0</v>
+      </c>
+      <c r="D664" s="1">
+        <v>161.0</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1">
+        <v>663.0</v>
+      </c>
+      <c r="B665" s="1">
+        <v>1187.0</v>
+      </c>
+      <c r="C665" s="1">
+        <v>1378.0</v>
+      </c>
+      <c r="D665" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="338">
   <si>
     <t>stream</t>
   </si>
@@ -12616,6 +12616,23 @@
         <v>337</v>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="1">
+        <v>664.0</v>
+      </c>
+      <c r="B666" s="1">
+        <v>1025.0</v>
+      </c>
+      <c r="C666" s="1">
+        <v>1366.0</v>
+      </c>
+      <c r="D666" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="339">
   <si>
     <t>stream</t>
   </si>
@@ -1025,6 +1025,9 @@
   </si>
   <si>
     <t>jc, wu</t>
+  </si>
+  <si>
+    <t>jc, toxic</t>
   </si>
 </sst>
 </file>
@@ -12633,6 +12636,23 @@
         <v>36</v>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" s="1">
+        <v>665.0</v>
+      </c>
+      <c r="B667" s="1">
+        <v>1186.0</v>
+      </c>
+      <c r="C667" s="1">
+        <v>1314.0</v>
+      </c>
+      <c r="D667" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="340">
   <si>
     <t>stream</t>
   </si>
@@ -1028,6 +1028,9 @@
   </si>
   <si>
     <t>jc, toxic</t>
+  </si>
+  <si>
+    <t>jc, chameleon, tf2</t>
   </si>
 </sst>
 </file>
@@ -12653,6 +12656,40 @@
         <v>338</v>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="1">
+        <v>666.0</v>
+      </c>
+      <c r="B668" s="1">
+        <v>1436.0</v>
+      </c>
+      <c r="C668" s="1">
+        <v>1643.0</v>
+      </c>
+      <c r="D668" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1">
+        <v>667.0</v>
+      </c>
+      <c r="B669" s="1">
+        <v>1353.0</v>
+      </c>
+      <c r="C669" s="1">
+        <v>1808.0</v>
+      </c>
+      <c r="D669" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="341">
   <si>
     <t>stream</t>
   </si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>jc, chameleon, tf2</t>
+  </si>
+  <si>
+    <t>jc, marbies, lol</t>
   </si>
 </sst>
 </file>
@@ -12690,6 +12693,23 @@
         <v>339</v>
       </c>
     </row>
+    <row r="670">
+      <c r="A670" s="1">
+        <v>668.0</v>
+      </c>
+      <c r="B670" s="1">
+        <v>1022.0</v>
+      </c>
+      <c r="C670" s="1">
+        <v>1349.0</v>
+      </c>
+      <c r="D670" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="341">
   <si>
     <t>stream</t>
   </si>
@@ -12710,6 +12710,23 @@
         <v>340</v>
       </c>
     </row>
+    <row r="671">
+      <c r="A671" s="1">
+        <v>669.0</v>
+      </c>
+      <c r="B671" s="1">
+        <v>1521.0</v>
+      </c>
+      <c r="C671" s="1">
+        <v>1885.0</v>
+      </c>
+      <c r="D671" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="344">
   <si>
     <t>stream</t>
   </si>
@@ -1034,6 +1034,15 @@
   </si>
   <si>
     <t>jc, marbies, lol</t>
+  </si>
+  <si>
+    <t>jc, cs, chameleon</t>
+  </si>
+  <si>
+    <t>jc, gta5</t>
+  </si>
+  <si>
+    <t>jc, cs, gta5</t>
   </si>
 </sst>
 </file>
@@ -12727,6 +12736,74 @@
         <v>15</v>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" s="1">
+        <v>670.0</v>
+      </c>
+      <c r="B672" s="1">
+        <v>1325.0</v>
+      </c>
+      <c r="C672" s="1">
+        <v>1693.0</v>
+      </c>
+      <c r="D672" s="1">
+        <v>130.0</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1">
+        <v>671.0</v>
+      </c>
+      <c r="B673" s="1">
+        <v>1271.0</v>
+      </c>
+      <c r="C673" s="1">
+        <v>1585.0</v>
+      </c>
+      <c r="D673" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1">
+        <v>672.0</v>
+      </c>
+      <c r="B674" s="1">
+        <v>1897.0</v>
+      </c>
+      <c r="C674" s="1">
+        <v>2270.0</v>
+      </c>
+      <c r="D674" s="1">
+        <v>263.0</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1">
+        <v>673.0</v>
+      </c>
+      <c r="B675" s="1">
+        <v>2023.0</v>
+      </c>
+      <c r="C675" s="1">
+        <v>2627.0</v>
+      </c>
+      <c r="D675" s="1">
+        <v>307.0</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="344">
   <si>
     <t>stream</t>
   </si>
@@ -12804,6 +12804,23 @@
         <v>343</v>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" s="1">
+        <v>674.0</v>
+      </c>
+      <c r="B676" s="1">
+        <v>2138.0</v>
+      </c>
+      <c r="C676" s="1">
+        <v>2601.0</v>
+      </c>
+      <c r="D676" s="1">
+        <v>189.0</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="345">
   <si>
     <t>stream</t>
   </si>
@@ -1043,6 +1043,9 @@
   </si>
   <si>
     <t>jc, cs, gta5</t>
+  </si>
+  <si>
+    <t>jc, acb, cs</t>
   </si>
 </sst>
 </file>
@@ -12821,6 +12824,77 @@
         <v>342</v>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="1">
+        <v>675.0</v>
+      </c>
+      <c r="B677" s="1">
+        <v>1768.0</v>
+      </c>
+      <c r="C677" s="1">
+        <v>2303.0</v>
+      </c>
+      <c r="D677" s="1">
+        <v>151.0</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1">
+        <v>676.0</v>
+      </c>
+      <c r="B678" s="1">
+        <v>1429.0</v>
+      </c>
+      <c r="C678" s="1">
+        <v>2323.0</v>
+      </c>
+      <c r="D678" s="1">
+        <v>239.0</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1">
+        <v>677.0</v>
+      </c>
+      <c r="B679" s="1">
+        <v>1501.0</v>
+      </c>
+      <c r="C679" s="1">
+        <v>1709.0</v>
+      </c>
+      <c r="D679" s="1">
+        <v>137.0</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1">
+        <v>678.0</v>
+      </c>
+      <c r="B680" s="1">
+        <v>1791.0</v>
+      </c>
+      <c r="C680" s="1">
+        <v>2269.0</v>
+      </c>
+      <c r="D680" s="1">
+        <v>229.0</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="346">
   <si>
     <t>stream</t>
   </si>
@@ -1046,6 +1046,9 @@
   </si>
   <si>
     <t>jc, acb, cs</t>
+  </si>
+  <si>
+    <t>jc, cs, pubg</t>
   </si>
 </sst>
 </file>
@@ -12893,7 +12896,55 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="1"/>
+      <c r="A681" s="1">
+        <v>679.0</v>
+      </c>
+      <c r="B681" s="1">
+        <v>1895.0</v>
+      </c>
+      <c r="C681" s="1">
+        <v>2371.0</v>
+      </c>
+      <c r="D681" s="1">
+        <v>153.0</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1">
+        <v>680.0</v>
+      </c>
+      <c r="B682" s="1">
+        <v>1908.0</v>
+      </c>
+      <c r="C682" s="1">
+        <v>2437.0</v>
+      </c>
+      <c r="D682" s="1">
+        <v>141.0</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1">
+        <v>681.0</v>
+      </c>
+      <c r="B683" s="1">
+        <v>1389.0</v>
+      </c>
+      <c r="C683" s="1">
+        <v>1675.0</v>
+      </c>
+      <c r="D683" s="1">
+        <v>192.0</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>345</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="347">
   <si>
     <t>stream</t>
   </si>
@@ -1049,6 +1049,9 @@
   </si>
   <si>
     <t>jc, cs, pubg</t>
+  </si>
+  <si>
+    <t>jc, gta5, cs</t>
   </si>
 </sst>
 </file>
@@ -12934,7 +12937,7 @@
         <v>681.0</v>
       </c>
       <c r="B683" s="1">
-        <v>1389.0</v>
+        <v>1401.0</v>
       </c>
       <c r="C683" s="1">
         <v>1675.0</v>
@@ -12944,6 +12947,40 @@
       </c>
       <c r="E683" s="1" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1">
+        <v>682.0</v>
+      </c>
+      <c r="B684" s="1">
+        <v>1415.0</v>
+      </c>
+      <c r="C684" s="1">
+        <v>1658.0</v>
+      </c>
+      <c r="D684" s="1">
+        <v>237.0</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1">
+        <v>683.0</v>
+      </c>
+      <c r="B685" s="1">
+        <v>1426.0</v>
+      </c>
+      <c r="C685" s="1">
+        <v>1703.0</v>
+      </c>
+      <c r="D685" s="1">
+        <v>265.0</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="348">
   <si>
     <t>stream</t>
   </si>
@@ -1052,6 +1052,9 @@
   </si>
   <si>
     <t>jc, gta5, cs</t>
+  </si>
+  <si>
+    <t>jc, cs, mc, pratfall</t>
   </si>
 </sst>
 </file>
@@ -12983,6 +12986,142 @@
         <v>10</v>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" s="1">
+        <v>684.0</v>
+      </c>
+      <c r="B686" s="1">
+        <v>1458.0</v>
+      </c>
+      <c r="C686" s="1">
+        <v>1860.0</v>
+      </c>
+      <c r="D686" s="1">
+        <v>329.0</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1">
+        <v>685.0</v>
+      </c>
+      <c r="B687" s="1">
+        <v>1146.0</v>
+      </c>
+      <c r="C687" s="1">
+        <v>1262.0</v>
+      </c>
+      <c r="D687" s="1">
+        <v>107.0</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1">
+        <v>686.0</v>
+      </c>
+      <c r="B688" s="1">
+        <v>1662.0</v>
+      </c>
+      <c r="C688" s="1">
+        <v>1923.0</v>
+      </c>
+      <c r="D688" s="1">
+        <v>154.0</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1">
+        <v>687.0</v>
+      </c>
+      <c r="B689" s="1">
+        <v>1530.0</v>
+      </c>
+      <c r="C689" s="1">
+        <v>2063.0</v>
+      </c>
+      <c r="D689" s="1">
+        <v>112.0</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1">
+        <v>688.0</v>
+      </c>
+      <c r="B690" s="1">
+        <v>1224.0</v>
+      </c>
+      <c r="C690" s="1">
+        <v>1368.0</v>
+      </c>
+      <c r="D690" s="1">
+        <v>155.0</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1">
+        <v>689.0</v>
+      </c>
+      <c r="B691" s="1">
+        <v>1337.0</v>
+      </c>
+      <c r="C691" s="1">
+        <v>1602.0</v>
+      </c>
+      <c r="D691" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1">
+        <v>690.0</v>
+      </c>
+      <c r="B692" s="1">
+        <v>1288.0</v>
+      </c>
+      <c r="C692" s="1">
+        <v>1715.0</v>
+      </c>
+      <c r="D692" s="1">
+        <v>166.0</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1">
+        <v>691.0</v>
+      </c>
+      <c r="B693" s="1">
+        <v>1215.0</v>
+      </c>
+      <c r="C693" s="1">
+        <v>1740.0</v>
+      </c>
+      <c r="D693" s="1">
+        <v>175.0</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="348">
   <si>
     <t>stream</t>
   </si>
@@ -13122,6 +13122,108 @@
         <v>130</v>
       </c>
     </row>
+    <row r="694">
+      <c r="A694" s="1">
+        <v>692.0</v>
+      </c>
+      <c r="B694" s="1">
+        <v>1219.0</v>
+      </c>
+      <c r="C694" s="1">
+        <v>144.0</v>
+      </c>
+      <c r="D694" s="1">
+        <v>143.0</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1">
+        <v>693.0</v>
+      </c>
+      <c r="B695" s="1">
+        <v>1123.0</v>
+      </c>
+      <c r="C695" s="1">
+        <v>1324.0</v>
+      </c>
+      <c r="D695" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1">
+        <v>694.0</v>
+      </c>
+      <c r="B696" s="1">
+        <v>1153.0</v>
+      </c>
+      <c r="C696" s="1">
+        <v>1384.0</v>
+      </c>
+      <c r="D696" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1">
+        <v>695.0</v>
+      </c>
+      <c r="B697" s="1">
+        <v>1561.0</v>
+      </c>
+      <c r="C697" s="1">
+        <v>1869.0</v>
+      </c>
+      <c r="D697" s="1">
+        <v>98.0</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1">
+        <v>696.0</v>
+      </c>
+      <c r="B698" s="1">
+        <v>1150.0</v>
+      </c>
+      <c r="C698" s="1">
+        <v>1371.0</v>
+      </c>
+      <c r="D698" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1">
+        <v>697.0</v>
+      </c>
+      <c r="B699" s="1">
+        <v>1221.0</v>
+      </c>
+      <c r="C699" s="1">
+        <v>1508.0</v>
+      </c>
+      <c r="D699" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="348">
   <si>
     <t>stream</t>
   </si>
@@ -13224,6 +13224,23 @@
         <v>130</v>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" s="1">
+        <v>698.0</v>
+      </c>
+      <c r="B700" s="1">
+        <v>1183.0</v>
+      </c>
+      <c r="C700" s="1">
+        <v>1919.0</v>
+      </c>
+      <c r="D700" s="1">
+        <v>116.0</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="348">
   <si>
     <t>stream</t>
   </si>
@@ -13241,6 +13241,23 @@
         <v>130</v>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" s="1">
+        <v>699.0</v>
+      </c>
+      <c r="B701" s="1">
+        <v>1050.0</v>
+      </c>
+      <c r="C701" s="1">
+        <v>1289.0</v>
+      </c>
+      <c r="D701" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="350">
   <si>
     <t>stream</t>
   </si>
@@ -1055,6 +1055,12 @@
   </si>
   <si>
     <t>jc, cs, mc, pratfall</t>
+  </si>
+  <si>
+    <t>jc, cs. mc</t>
+  </si>
+  <si>
+    <t>jc, cs, acb</t>
   </si>
 </sst>
 </file>
@@ -13258,6 +13264,145 @@
         <v>23</v>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" s="1">
+        <v>700.0</v>
+      </c>
+      <c r="B702" s="1">
+        <v>1140.0</v>
+      </c>
+      <c r="C702" s="1">
+        <v>1382.0</v>
+      </c>
+      <c r="D702" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1">
+        <v>701.0</v>
+      </c>
+      <c r="B703" s="1">
+        <v>1142.0</v>
+      </c>
+      <c r="C703" s="1">
+        <v>1268.0</v>
+      </c>
+      <c r="D703" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1">
+        <v>702.0</v>
+      </c>
+      <c r="B704" s="1">
+        <v>954.0</v>
+      </c>
+      <c r="C704" s="1">
+        <v>1263.0</v>
+      </c>
+      <c r="D704" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1">
+        <v>703.0</v>
+      </c>
+      <c r="B705" s="1">
+        <v>1208.0</v>
+      </c>
+      <c r="C705" s="1">
+        <v>1328.0</v>
+      </c>
+      <c r="D705" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1">
+        <v>704.0</v>
+      </c>
+      <c r="B706" s="1">
+        <v>1267.0</v>
+      </c>
+      <c r="C706" s="1">
+        <v>1998.0</v>
+      </c>
+      <c r="D706" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1">
+        <v>705.0</v>
+      </c>
+      <c r="B707" s="1">
+        <v>864.0</v>
+      </c>
+      <c r="C707" s="1">
+        <v>993.0</v>
+      </c>
+      <c r="D707" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1">
+        <v>706.0</v>
+      </c>
+      <c r="B708" s="1">
+        <v>1546.0</v>
+      </c>
+      <c r="C708" s="1">
+        <v>1844.0</v>
+      </c>
+      <c r="D708" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1">
+        <v>707.0</v>
+      </c>
+      <c r="B709" s="1">
+        <v>1211.0</v>
+      </c>
+      <c r="C709" s="1">
+        <v>1425.0</v>
+      </c>
+      <c r="D709" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="351">
   <si>
     <t>stream</t>
   </si>
@@ -1061,6 +1061,9 @@
   </si>
   <si>
     <t>jc, cs, acb</t>
+  </si>
+  <si>
+    <t>cs, irl</t>
   </si>
 </sst>
 </file>
@@ -13401,7 +13404,21 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" s="1"/>
+      <c r="A710" s="1">
+        <v>708.0</v>
+      </c>
+      <c r="B710" s="1">
+        <v>1151.0</v>
+      </c>
+      <c r="C710" s="1">
+        <v>1563.0</v>
+      </c>
+      <c r="D710" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>350</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="351">
   <si>
     <t>stream</t>
   </si>
@@ -13420,6 +13420,23 @@
         <v>350</v>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="1">
+        <v>709.0</v>
+      </c>
+      <c r="B711" s="1">
+        <v>1241.0</v>
+      </c>
+      <c r="C711" s="1">
+        <v>1393.0</v>
+      </c>
+      <c r="D711" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="351">
   <si>
     <t>stream</t>
   </si>
@@ -13437,6 +13437,23 @@
         <v>27</v>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" s="1">
+        <v>710.0</v>
+      </c>
+      <c r="B712" s="1">
+        <v>1497.0</v>
+      </c>
+      <c r="C712" s="1">
+        <v>1749.0</v>
+      </c>
+      <c r="D712" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="352">
   <si>
     <t>stream</t>
   </si>
@@ -1064,6 +1064,9 @@
   </si>
   <si>
     <t>cs, irl</t>
+  </si>
+  <si>
+    <t>jc, cs, plague</t>
   </si>
 </sst>
 </file>
@@ -13454,6 +13457,40 @@
         <v>27</v>
       </c>
     </row>
+    <row r="713">
+      <c r="A713" s="1">
+        <v>711.0</v>
+      </c>
+      <c r="B713" s="1">
+        <v>975.0</v>
+      </c>
+      <c r="C713" s="1">
+        <v>1068.0</v>
+      </c>
+      <c r="D713" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1">
+        <v>712.0</v>
+      </c>
+      <c r="B714" s="1">
+        <v>1219.0</v>
+      </c>
+      <c r="C714" s="1">
+        <v>1924.0</v>
+      </c>
+      <c r="D714" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/DorozeaStreamStats.xlsx
+++ b/DorozeaStreamStats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="352">
   <si>
     <t>stream</t>
   </si>
@@ -13491,6 +13491,57 @@
         <v>36</v>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" s="1">
+        <v>713.0</v>
+      </c>
+      <c r="B715" s="1">
+        <v>1110.0</v>
+      </c>
+      <c r="C715" s="1">
+        <v>1323.0</v>
+      </c>
+      <c r="D715" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1">
+        <v>714.0</v>
+      </c>
+      <c r="B716" s="1">
+        <v>949.0</v>
+      </c>
+      <c r="C716" s="1">
+        <v>1170.0</v>
+      </c>
+      <c r="D716" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1">
+        <v>715.0</v>
+      </c>
+      <c r="B717" s="1">
+        <v>1066.0</v>
+      </c>
+      <c r="C717" s="1">
+        <v>1253.0</v>
+      </c>
+      <c r="D717" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
